--- a/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB66E646-E57E-4C3E-A494-54E1CFF37947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B668A37-998E-4275-B25C-F4D4429DBB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="3990" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataPattern" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Datetime</t>
+  </si>
+  <si>
+    <t>dd/MM/yyyy</t>
+  </si>
+  <si>
+    <t>Cases</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
   <si>
     <t>TestCaseID</t>
   </si>
@@ -42,51 +60,33 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Data Type</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Datetime</t>
-  </si>
-  <si>
-    <t>dd/MM/yyyy</t>
-  </si>
-  <si>
-    <t>Cases</t>
-  </si>
-  <si>
-    <t>Mark</t>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>webbased</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value</t>
+    <t>Protocol</t>
+  </si>
+  <si>
+    <t>HTTP/TCP</t>
+  </si>
+  <si>
+    <t>Console</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -157,18 +157,18 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -452,27 +452,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="2" width="22.25" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="1" max="1" width="18.36328125" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -484,17 +484,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -505,27 +505,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="44.375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="5"/>
+    <col min="1" max="1" width="10.6328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="44.36328125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="8.90625" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
     </row>
@@ -537,26 +537,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C6C48B-55C0-4A7D-A267-4474B31A4631}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
+      <c r="B3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B668A37-998E-4275-B25C-F4D4429DBB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E0466-22FF-46A2-A9BA-89307440A7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataPattern" sheetId="3" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -155,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -164,12 +162,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="5" customWidth="1"/>
@@ -521,14 +513,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/Question/Header.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E0466-22FF-46A2-A9BA-89307440A7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3450CD37-89CA-4D28-909B-932B00AEE10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataPattern" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Data Type</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Console</t>
+  </si>
+  <si>
+    <t>Grade_Content</t>
+  </si>
+  <si>
+    <t>Client/Server</t>
   </si>
 </sst>
 </file>
@@ -444,14 +450,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.36328125" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" customWidth="1"/>
-    <col min="3" max="3" width="21.90625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -476,12 +482,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -497,15 +503,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="44.36328125" style="5" customWidth="1"/>
-    <col min="3" max="4" width="8.90625" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="5"/>
+    <col min="1" max="1" width="10.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
@@ -521,13 +527,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C6C48B-55C0-4A7D-A267-4474B31A4631}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -535,7 +542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -543,12 +550,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
